--- a/backend/data/financials_by_company/10X.AX.xlsx
+++ b/backend/data/financials_by_company/10X.AX.xlsx
@@ -1675,10 +1675,8 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1877,7 +1875,7 @@
         <v>-183026</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-0.02702701</v>
@@ -1974,7 +1972,7 @@
         </is>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0.0076999962</v>
